--- a/Lora_and_SigFox_Devices/MeteoHelix_IoT_Pro_Gen2/20250603_MeteoHelix_IoT_Pro_Gen2_payloads_LOCKED.xlsx
+++ b/Lora_and_SigFox_Devices/MeteoHelix_IoT_Pro_Gen2/20250603_MeteoHelix_IoT_Pro_Gen2_payloads_LOCKED.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Documents\GitHub\P_SRC_device_decoders\Lora_and_SigFox_Devices\MeteoHelix_IoT_Pro_Gen2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Desktop\MeteoHelix_IoT_Pro_Gen2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2724AA8C-A2C4-4B14-9F62-80297D13E1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2743CC-A0A9-46E9-98F6-6BB1B10D789E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="152">
   <si>
     <t>This calculator is meant for quick message decoding for MeteoWind IoT wind transmitters that send a bit-shifted string.</t>
   </si>
@@ -730,12 +730,6 @@
   </si>
   <si>
     <t>Irr_max &amp; Irr_min values are absolute numbers (do NOT get subtracted or added to the Irradiation reading).</t>
-  </si>
-  <si>
-    <t>Battery value changes based on Index. Index=0:4 -&gt; =IF(MOD(B11,10)&lt;=4,MOD(B11,10)*C13+C16,MOD(B11,10)*C13+C16-1)
-Every other message will have the correct voltage. If FFFF is sent (4) = invalid value. 
-With Bat_min = 3.3V, possible bvalues are 3.3(0), 3.4(1), 3.5(2), 3.6(3),error((4). 
-With Bat_min = 3.7V, possible bvalues are 3.7(0), 3.8(1), 3.9(2), 4.0(3),error((4).</t>
   </si>
   <si>
     <t>Hardware type - 0=test, 1=MeteoHelix, 2=MeteoWind, 3=MeteoRain, 4=MeteoAG, …</t>
@@ -1958,22 +1952,7 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1988,21 +1967,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2021,6 +2006,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2549,7 +2543,7 @@
         <v>70</v>
       </c>
       <c r="B5" s="198" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" s="199"/>
       <c r="D5" s="199"/>
@@ -2690,10 +2684,10 @@
         <v>84</v>
       </c>
       <c r="O8" s="80" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P8" s="81" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q8" s="78"/>
     </row>
@@ -3612,9 +3606,7 @@
       <c r="Z24" s="132"/>
     </row>
     <row r="25" spans="1:29" s="72" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="204" t="s">
-        <v>145</v>
-      </c>
+      <c r="A25" s="204"/>
       <c r="B25" s="204"/>
       <c r="C25" s="204"/>
       <c r="D25" s="204"/>
@@ -4352,7 +4344,7 @@
       <c r="Z37" s="71"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TYMvIQbGbWIsLzqbIJxmuxy2RgiRDVtx7qcPildj5gBmbIfvzfzM1z9Y3IfJLQdyy1uShPYkHuV5vwXk8u7eNA==" saltValue="CtpbAtgdSG8OTbxPnUvRyQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EDu8rde8jPuoQMGm0dtpOMPdHAr0e+B4qT42LYsp+2cT6/l6A+DA9AiIOqXbzbD7iLJhk8ZDBa3Um8YOlPsnOA==" saltValue="Y0iMtk99pSU8fnCX4WsE1w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="15">
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:E37"/>
@@ -4409,33 +4401,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" s="140" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="213" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
-      <c r="J1" s="208"/>
-      <c r="K1" s="208"/>
-      <c r="L1" s="208"/>
-      <c r="M1" s="208"/>
-      <c r="N1" s="208"/>
-      <c r="O1" s="208"/>
-      <c r="P1" s="208"/>
-      <c r="Q1" s="208"/>
-      <c r="R1" s="208"/>
-      <c r="S1" s="208"/>
-      <c r="T1" s="208"/>
-      <c r="U1" s="208"/>
-      <c r="V1" s="208"/>
-      <c r="W1" s="208"/>
-      <c r="X1" s="208"/>
-      <c r="Y1" s="208"/>
+      <c r="B1" s="213"/>
+      <c r="C1" s="213"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="213"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="213"/>
+      <c r="P1" s="213"/>
+      <c r="Q1" s="213"/>
+      <c r="R1" s="213"/>
+      <c r="S1" s="213"/>
+      <c r="T1" s="213"/>
+      <c r="U1" s="213"/>
+      <c r="V1" s="213"/>
+      <c r="W1" s="213"/>
+      <c r="X1" s="213"/>
+      <c r="Y1" s="213"/>
       <c r="Z1" s="139"/>
       <c r="AA1" s="139"/>
       <c r="AB1" s="139"/>
@@ -5437,21 +5429,21 @@
       <c r="AMJ1" s="139"/>
     </row>
     <row r="2" spans="1:1024" s="140" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="209" t="s">
+      <c r="A2" s="214" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="209"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="209"/>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="M2" s="209"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
+      <c r="L2" s="214"/>
+      <c r="M2" s="214"/>
       <c r="N2" s="141"/>
       <c r="O2" s="141"/>
       <c r="P2" s="141"/>
@@ -6465,20 +6457,20 @@
       <c r="AMJ2" s="139"/>
     </row>
     <row r="3" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="210" t="s">
+      <c r="A3" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="210"/>
-      <c r="C3" s="210"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="207"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="207"/>
       <c r="M3" s="142"/>
       <c r="N3" s="142"/>
       <c r="O3" s="143"/>
@@ -8526,23 +8518,23 @@
       <c r="A5" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="211" t="str">
+      <c r="B5" s="215" t="str">
         <f>CONCATENATE(B34,C34,D34,E34,F34,G34,H34,I34,J34,K34,L34,M34,N34,O34,P34,Q34,R34,S34,T34,U34,V34,W34,X34,Y34,Z34,AA34,AB34,AC34,AD34,AE34,AF34,AG34,AH34,AI34,AJ34,AK34)</f>
         <v>000000001101000010011000110010111001000101000000010000000000000010000011011000000000000000000000000000000000000000000000000000000000000000000000</v>
       </c>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
-      <c r="N5" s="211"/>
-      <c r="O5" s="211"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="215"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="215"/>
+      <c r="K5" s="215"/>
+      <c r="L5" s="215"/>
+      <c r="M5" s="215"/>
+      <c r="N5" s="215"/>
+      <c r="O5" s="215"/>
       <c r="P5" s="139"/>
       <c r="Q5" s="139"/>
       <c r="R5" s="139"/>
@@ -23258,49 +23250,49 @@
       <c r="AME21" s="139"/>
     </row>
     <row r="22" spans="1:1024" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="207" t="s">
+      <c r="A22" s="212" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="207"/>
-      <c r="C22" s="207"/>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
-      <c r="F22" s="207"/>
-      <c r="G22" s="207"/>
-      <c r="H22" s="207"/>
-      <c r="I22" s="207"/>
-      <c r="J22" s="207"/>
-      <c r="K22" s="207"/>
-      <c r="L22" s="207"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="212"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="212"/>
+      <c r="F22" s="212"/>
+      <c r="G22" s="212"/>
+      <c r="H22" s="212"/>
+      <c r="I22" s="212"/>
+      <c r="J22" s="212"/>
+      <c r="K22" s="212"/>
+      <c r="L22" s="212"/>
     </row>
     <row r="23" spans="1:1024" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="212" t="s">
+      <c r="A23" s="216" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="212"/>
-      <c r="C23" s="212"/>
-      <c r="D23" s="212"/>
-      <c r="E23" s="212"/>
-      <c r="F23" s="212"/>
-      <c r="G23" s="212"/>
-      <c r="H23" s="212"/>
-      <c r="I23" s="212"/>
-      <c r="J23" s="212"/>
-      <c r="K23" s="212"/>
-      <c r="L23" s="212"/>
-      <c r="M23" s="212"/>
-      <c r="N23" s="212"/>
-      <c r="O23" s="212"/>
-      <c r="P23" s="212"/>
-      <c r="Q23" s="212"/>
-      <c r="R23" s="212"/>
-      <c r="S23" s="212"/>
-      <c r="T23" s="212"/>
-      <c r="U23" s="212"/>
-      <c r="V23" s="212"/>
-      <c r="W23" s="212"/>
-      <c r="X23" s="212"/>
-      <c r="Y23" s="212"/>
+      <c r="B23" s="216"/>
+      <c r="C23" s="216"/>
+      <c r="D23" s="216"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="216"/>
+      <c r="G23" s="216"/>
+      <c r="H23" s="216"/>
+      <c r="I23" s="216"/>
+      <c r="J23" s="216"/>
+      <c r="K23" s="216"/>
+      <c r="L23" s="216"/>
+      <c r="M23" s="216"/>
+      <c r="N23" s="216"/>
+      <c r="O23" s="216"/>
+      <c r="P23" s="216"/>
+      <c r="Q23" s="216"/>
+      <c r="R23" s="216"/>
+      <c r="S23" s="216"/>
+      <c r="T23" s="216"/>
+      <c r="U23" s="216"/>
+      <c r="V23" s="216"/>
+      <c r="W23" s="216"/>
+      <c r="X23" s="216"/>
+      <c r="Y23" s="216"/>
     </row>
     <row r="24" spans="1:1024" s="178" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="204" t="s">
@@ -23332,36 +23324,36 @@
       <c r="Y24" s="134"/>
     </row>
     <row r="25" spans="1:1024" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="207" t="s">
+      <c r="A25" s="212" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="207"/>
-      <c r="C25" s="207"/>
-      <c r="D25" s="207"/>
-      <c r="E25" s="207"/>
-      <c r="F25" s="207"/>
-      <c r="G25" s="207"/>
-      <c r="H25" s="207"/>
-      <c r="I25" s="207"/>
-      <c r="J25" s="207"/>
-      <c r="K25" s="207"/>
-      <c r="L25" s="207"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="212"/>
+      <c r="D25" s="212"/>
+      <c r="E25" s="212"/>
+      <c r="F25" s="212"/>
+      <c r="G25" s="212"/>
+      <c r="H25" s="212"/>
+      <c r="I25" s="212"/>
+      <c r="J25" s="212"/>
+      <c r="K25" s="212"/>
+      <c r="L25" s="212"/>
     </row>
     <row r="26" spans="1:1024" s="178" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="210" t="s">
+      <c r="A26" s="207" t="s">
         <v>95</v>
       </c>
-      <c r="B26" s="210"/>
-      <c r="C26" s="210"/>
-      <c r="D26" s="210"/>
-      <c r="E26" s="210"/>
-      <c r="F26" s="210"/>
-      <c r="G26" s="210"/>
-      <c r="H26" s="210"/>
-      <c r="I26" s="210"/>
-      <c r="J26" s="210"/>
-      <c r="K26" s="210"/>
-      <c r="L26" s="210"/>
+      <c r="B26" s="207"/>
+      <c r="C26" s="207"/>
+      <c r="D26" s="207"/>
+      <c r="E26" s="207"/>
+      <c r="F26" s="207"/>
+      <c r="G26" s="207"/>
+      <c r="H26" s="207"/>
+      <c r="I26" s="207"/>
+      <c r="J26" s="207"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="207"/>
     </row>
     <row r="27" spans="1:1024" s="178" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="205" t="s">
@@ -23398,18 +23390,18 @@
       <c r="L28" s="179"/>
     </row>
     <row r="29" spans="1:1024" s="180" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="210"/>
-      <c r="B29" s="210"/>
-      <c r="C29" s="210"/>
-      <c r="D29" s="210"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="210"/>
-      <c r="G29" s="210"/>
-      <c r="H29" s="210"/>
-      <c r="I29" s="210"/>
-      <c r="J29" s="210"/>
-      <c r="K29" s="210"/>
-      <c r="L29" s="210"/>
+      <c r="A29" s="207"/>
+      <c r="B29" s="207"/>
+      <c r="C29" s="207"/>
+      <c r="D29" s="207"/>
+      <c r="E29" s="207"/>
+      <c r="F29" s="207"/>
+      <c r="G29" s="207"/>
+      <c r="H29" s="207"/>
+      <c r="I29" s="207"/>
+      <c r="J29" s="207"/>
+      <c r="K29" s="207"/>
+      <c r="L29" s="207"/>
     </row>
     <row r="30" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="139"/>
@@ -24438,33 +24430,33 @@
       <c r="AMJ30" s="139"/>
     </row>
     <row r="31" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="213" t="s">
+      <c r="A31" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="213"/>
-      <c r="C31" s="213"/>
-      <c r="D31" s="213"/>
-      <c r="E31" s="213"/>
-      <c r="F31" s="213"/>
-      <c r="G31" s="213"/>
-      <c r="H31" s="213"/>
-      <c r="I31" s="213"/>
-      <c r="J31" s="213"/>
-      <c r="K31" s="213"/>
-      <c r="L31" s="213"/>
-      <c r="M31" s="213"/>
-      <c r="N31" s="213"/>
-      <c r="O31" s="213"/>
-      <c r="P31" s="213"/>
-      <c r="Q31" s="213"/>
-      <c r="R31" s="213"/>
-      <c r="S31" s="213"/>
-      <c r="T31" s="213"/>
-      <c r="U31" s="213"/>
-      <c r="V31" s="213"/>
-      <c r="W31" s="213"/>
-      <c r="X31" s="213"/>
-      <c r="Y31" s="213"/>
+      <c r="B31" s="208"/>
+      <c r="C31" s="208"/>
+      <c r="D31" s="208"/>
+      <c r="E31" s="208"/>
+      <c r="F31" s="208"/>
+      <c r="G31" s="208"/>
+      <c r="H31" s="208"/>
+      <c r="I31" s="208"/>
+      <c r="J31" s="208"/>
+      <c r="K31" s="208"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="208"/>
+      <c r="N31" s="208"/>
+      <c r="O31" s="208"/>
+      <c r="P31" s="208"/>
+      <c r="Q31" s="208"/>
+      <c r="R31" s="208"/>
+      <c r="S31" s="208"/>
+      <c r="T31" s="208"/>
+      <c r="U31" s="208"/>
+      <c r="V31" s="208"/>
+      <c r="W31" s="208"/>
+      <c r="X31" s="208"/>
+      <c r="Y31" s="208"/>
       <c r="Z31" s="139"/>
       <c r="AA31" s="139"/>
       <c r="AB31" s="139"/>
@@ -29864,26 +29856,26 @@
       <c r="AMJ35" s="139"/>
     </row>
     <row r="36" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="214" t="s">
+      <c r="A36" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="214"/>
-      <c r="C36" s="215" t="s">
+      <c r="B36" s="209"/>
+      <c r="C36" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="215"/>
-      <c r="E36" s="215"/>
-      <c r="F36" s="216" t="s">
+      <c r="D36" s="210"/>
+      <c r="E36" s="210"/>
+      <c r="F36" s="211" t="s">
         <v>31</v>
       </c>
-      <c r="G36" s="216"/>
-      <c r="H36" s="215" t="s">
+      <c r="G36" s="211"/>
+      <c r="H36" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="215"/>
-      <c r="J36" s="215"/>
-      <c r="K36" s="215"/>
-      <c r="L36" s="215"/>
+      <c r="I36" s="210"/>
+      <c r="J36" s="210"/>
+      <c r="K36" s="210"/>
+      <c r="L36" s="210"/>
       <c r="M36" s="181"/>
       <c r="N36" s="181"/>
       <c r="O36" s="181"/>
@@ -30900,12 +30892,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="/+Q9kyksrTSdXm7mftVB0Ju1dh2CQyPJVTE1SAmC0JLSmAQkMPnAZAIUIZBeMC/BPay5LJhQWhS2A6qfv6EqlQ==" saltValue="paqyyi4+K/xj45pGqvZirw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="16">
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A31:Y31"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:L36"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A27:L27"/>
@@ -30916,6 +30902,12 @@
     <mergeCell ref="A23:Y23"/>
     <mergeCell ref="A26:L26"/>
     <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:L36"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <hyperlinks>
@@ -30954,33 +30946,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" s="140" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="213" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
-      <c r="J1" s="208"/>
-      <c r="K1" s="208"/>
-      <c r="L1" s="208"/>
-      <c r="M1" s="208"/>
-      <c r="N1" s="208"/>
-      <c r="O1" s="208"/>
-      <c r="P1" s="208"/>
-      <c r="Q1" s="208"/>
-      <c r="R1" s="208"/>
-      <c r="S1" s="208"/>
-      <c r="T1" s="208"/>
-      <c r="U1" s="208"/>
-      <c r="V1" s="208"/>
-      <c r="W1" s="208"/>
-      <c r="X1" s="208"/>
-      <c r="Y1" s="208"/>
+      <c r="B1" s="213"/>
+      <c r="C1" s="213"/>
+      <c r="D1" s="213"/>
+      <c r="E1" s="213"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
+      <c r="I1" s="213"/>
+      <c r="J1" s="213"/>
+      <c r="K1" s="213"/>
+      <c r="L1" s="213"/>
+      <c r="M1" s="213"/>
+      <c r="N1" s="213"/>
+      <c r="O1" s="213"/>
+      <c r="P1" s="213"/>
+      <c r="Q1" s="213"/>
+      <c r="R1" s="213"/>
+      <c r="S1" s="213"/>
+      <c r="T1" s="213"/>
+      <c r="U1" s="213"/>
+      <c r="V1" s="213"/>
+      <c r="W1" s="213"/>
+      <c r="X1" s="213"/>
+      <c r="Y1" s="213"/>
       <c r="Z1" s="139"/>
       <c r="AA1" s="139"/>
       <c r="AB1" s="139"/>
@@ -31982,21 +31974,21 @@
       <c r="AMJ1" s="139"/>
     </row>
     <row r="2" spans="1:1024" s="140" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="209" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="209"/>
-      <c r="C2" s="209"/>
-      <c r="D2" s="209"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="209"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="209"/>
-      <c r="I2" s="209"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="209"/>
-      <c r="M2" s="209"/>
+      <c r="A2" s="214" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="214"/>
+      <c r="G2" s="214"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="214"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="214"/>
+      <c r="L2" s="214"/>
+      <c r="M2" s="214"/>
       <c r="N2" s="141"/>
       <c r="O2" s="141">
         <f>2^8</f>
@@ -33013,20 +33005,20 @@
       <c r="AMJ2" s="139"/>
     </row>
     <row r="3" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="210" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" s="210"/>
-      <c r="C3" s="210"/>
-      <c r="D3" s="210"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
+      <c r="A3" s="207" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="207"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="207"/>
       <c r="M3" s="142"/>
       <c r="N3" s="142"/>
       <c r="O3" s="142"/>
@@ -34044,19 +34036,19 @@
       <c r="A4" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="218" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="217"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
       <c r="M4" s="139"/>
       <c r="N4" s="139"/>
       <c r="O4" s="139"/>
@@ -35074,23 +35066,23 @@
       <c r="A5" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="211" t="str">
+      <c r="B5" s="215" t="str">
         <f>CONCATENATE(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,O38,P38,Q38,R38,S38,T38,U38,V38,W38,X38,Y38,Z38,AA38,AB38,AC38,AD38,AE38,AF38,AG38,AH38,AI38,AJ38,AK38)</f>
         <v>110001011000001010100001000010000111000001010000100100000100101100110001000101000000000000000000000000000000000000000000000000000000000000000000</v>
       </c>
-      <c r="C5" s="211"/>
-      <c r="D5" s="211"/>
-      <c r="E5" s="211"/>
-      <c r="F5" s="211"/>
-      <c r="G5" s="211"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="211"/>
-      <c r="K5" s="211"/>
-      <c r="L5" s="211"/>
-      <c r="M5" s="211"/>
-      <c r="N5" s="211"/>
-      <c r="O5" s="211"/>
+      <c r="C5" s="215"/>
+      <c r="D5" s="215"/>
+      <c r="E5" s="215"/>
+      <c r="F5" s="215"/>
+      <c r="G5" s="215"/>
+      <c r="H5" s="215"/>
+      <c r="I5" s="215"/>
+      <c r="J5" s="215"/>
+      <c r="K5" s="215"/>
+      <c r="L5" s="215"/>
+      <c r="M5" s="215"/>
+      <c r="N5" s="215"/>
+      <c r="O5" s="215"/>
       <c r="P5" s="139"/>
       <c r="Q5" s="139"/>
       <c r="R5" s="139"/>
@@ -48835,32 +48827,32 @@
       <c r="AMF20" s="139"/>
     </row>
     <row r="21" spans="1:1020" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="207" t="s">
+      <c r="A21" s="212" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="207"/>
-      <c r="C21" s="207"/>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
-      <c r="F21" s="207"/>
-      <c r="G21" s="207"/>
-      <c r="H21" s="207"/>
-      <c r="I21" s="207"/>
-      <c r="J21" s="207"/>
-      <c r="K21" s="207"/>
-      <c r="L21" s="207"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="212"/>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="212"/>
+      <c r="G21" s="212"/>
+      <c r="H21" s="212"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="212"/>
+      <c r="L21" s="212"/>
     </row>
     <row r="22" spans="1:1020" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="207" t="s">
+      <c r="A22" s="212" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="207"/>
-      <c r="C22" s="207"/>
-      <c r="D22" s="207"/>
-      <c r="E22" s="207"/>
-      <c r="F22" s="207"/>
-      <c r="G22" s="207"/>
-      <c r="H22" s="207"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="212"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="212"/>
+      <c r="F22" s="212"/>
+      <c r="G22" s="212"/>
+      <c r="H22" s="212"/>
       <c r="J22" s="190" t="s">
         <v>64</v>
       </c>
@@ -48949,46 +48941,46 @@
       <c r="A28" s="179"/>
     </row>
     <row r="29" spans="1:1020" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="207"/>
-      <c r="B29" s="207"/>
-      <c r="C29" s="207"/>
-      <c r="D29" s="207"/>
-      <c r="E29" s="207"/>
-      <c r="F29" s="207"/>
-      <c r="G29" s="207"/>
-      <c r="H29" s="207"/>
-      <c r="I29" s="207"/>
-      <c r="J29" s="207"/>
-      <c r="K29" s="207"/>
-      <c r="L29" s="207"/>
+      <c r="A29" s="212"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="212"/>
+      <c r="D29" s="212"/>
+      <c r="E29" s="212"/>
+      <c r="F29" s="212"/>
+      <c r="G29" s="212"/>
+      <c r="H29" s="212"/>
+      <c r="I29" s="212"/>
+      <c r="J29" s="212"/>
+      <c r="K29" s="212"/>
+      <c r="L29" s="212"/>
     </row>
     <row r="30" spans="1:1020" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="207"/>
-      <c r="B30" s="207"/>
-      <c r="C30" s="207"/>
-      <c r="D30" s="207"/>
-      <c r="E30" s="207"/>
-      <c r="F30" s="207"/>
-      <c r="G30" s="207"/>
-      <c r="H30" s="207"/>
-      <c r="I30" s="207"/>
-      <c r="J30" s="207"/>
-      <c r="K30" s="207"/>
-      <c r="L30" s="207"/>
+      <c r="A30" s="212"/>
+      <c r="B30" s="212"/>
+      <c r="C30" s="212"/>
+      <c r="D30" s="212"/>
+      <c r="E30" s="212"/>
+      <c r="F30" s="212"/>
+      <c r="G30" s="212"/>
+      <c r="H30" s="212"/>
+      <c r="I30" s="212"/>
+      <c r="J30" s="212"/>
+      <c r="K30" s="212"/>
+      <c r="L30" s="212"/>
     </row>
     <row r="31" spans="1:1020" s="178" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="207"/>
-      <c r="B31" s="207"/>
-      <c r="C31" s="207"/>
-      <c r="D31" s="207"/>
-      <c r="E31" s="207"/>
-      <c r="F31" s="207"/>
-      <c r="G31" s="207"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="207"/>
-      <c r="J31" s="207"/>
-      <c r="K31" s="207"/>
-      <c r="L31" s="207"/>
+      <c r="A31" s="212"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="212"/>
+      <c r="D31" s="212"/>
+      <c r="E31" s="212"/>
+      <c r="F31" s="212"/>
+      <c r="G31" s="212"/>
+      <c r="H31" s="212"/>
+      <c r="I31" s="212"/>
+      <c r="J31" s="212"/>
+      <c r="K31" s="212"/>
+      <c r="L31" s="212"/>
     </row>
     <row r="32" spans="1:1020" s="180" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="205" t="s">
@@ -49007,20 +48999,20 @@
       <c r="L32" s="205"/>
     </row>
     <row r="33" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="218" t="s">
+      <c r="A33" s="217" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="218"/>
-      <c r="C33" s="218"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="218"/>
-      <c r="F33" s="218"/>
-      <c r="G33" s="218"/>
-      <c r="H33" s="218"/>
-      <c r="I33" s="218"/>
-      <c r="J33" s="218"/>
-      <c r="K33" s="218"/>
-      <c r="L33" s="218"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="217"/>
+      <c r="L33" s="217"/>
       <c r="M33" s="181"/>
       <c r="N33" s="181"/>
       <c r="O33" s="181"/>
@@ -50035,20 +50027,20 @@
       <c r="AMJ33" s="139"/>
     </row>
     <row r="34" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="218" t="s">
+      <c r="A34" s="217" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="218"/>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
+      <c r="B34" s="217"/>
+      <c r="C34" s="217"/>
+      <c r="D34" s="217"/>
+      <c r="E34" s="217"/>
+      <c r="F34" s="217"/>
+      <c r="G34" s="217"/>
+      <c r="H34" s="217"/>
+      <c r="I34" s="217"/>
+      <c r="J34" s="217"/>
+      <c r="K34" s="217"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="181"/>
       <c r="N34" s="181"/>
       <c r="O34" s="181"/>
@@ -51063,33 +51055,33 @@
       <c r="AMJ34" s="139"/>
     </row>
     <row r="35" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="213" t="s">
+      <c r="A35" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="213"/>
-      <c r="C35" s="213"/>
-      <c r="D35" s="213"/>
-      <c r="E35" s="213"/>
-      <c r="F35" s="213"/>
-      <c r="G35" s="213"/>
-      <c r="H35" s="213"/>
-      <c r="I35" s="213"/>
-      <c r="J35" s="213"/>
-      <c r="K35" s="213"/>
-      <c r="L35" s="213"/>
-      <c r="M35" s="213"/>
-      <c r="N35" s="213"/>
-      <c r="O35" s="213"/>
-      <c r="P35" s="213"/>
-      <c r="Q35" s="213"/>
-      <c r="R35" s="213"/>
-      <c r="S35" s="213"/>
-      <c r="T35" s="213"/>
-      <c r="U35" s="213"/>
-      <c r="V35" s="213"/>
-      <c r="W35" s="213"/>
-      <c r="X35" s="213"/>
-      <c r="Y35" s="213"/>
+      <c r="B35" s="208"/>
+      <c r="C35" s="208"/>
+      <c r="D35" s="208"/>
+      <c r="E35" s="208"/>
+      <c r="F35" s="208"/>
+      <c r="G35" s="208"/>
+      <c r="H35" s="208"/>
+      <c r="I35" s="208"/>
+      <c r="J35" s="208"/>
+      <c r="K35" s="208"/>
+      <c r="L35" s="208"/>
+      <c r="M35" s="208"/>
+      <c r="N35" s="208"/>
+      <c r="O35" s="208"/>
+      <c r="P35" s="208"/>
+      <c r="Q35" s="208"/>
+      <c r="R35" s="208"/>
+      <c r="S35" s="208"/>
+      <c r="T35" s="208"/>
+      <c r="U35" s="208"/>
+      <c r="V35" s="208"/>
+      <c r="W35" s="208"/>
+      <c r="X35" s="208"/>
+      <c r="Y35" s="208"/>
       <c r="Z35" s="139"/>
       <c r="AA35" s="139"/>
       <c r="AB35" s="139"/>
@@ -56489,26 +56481,26 @@
       <c r="AMJ39" s="139"/>
     </row>
     <row r="40" spans="1:1024" s="140" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="214"/>
-      <c r="C40" s="215" t="s">
+      <c r="B40" s="209"/>
+      <c r="C40" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="215"/>
-      <c r="E40" s="215"/>
-      <c r="F40" s="216" t="s">
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="211" t="s">
         <v>31</v>
       </c>
-      <c r="G40" s="216"/>
-      <c r="H40" s="215" t="s">
+      <c r="G40" s="211"/>
+      <c r="H40" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="I40" s="215"/>
-      <c r="J40" s="215"/>
-      <c r="K40" s="215"/>
-      <c r="L40" s="215"/>
+      <c r="I40" s="210"/>
+      <c r="J40" s="210"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="210"/>
       <c r="M40" s="181"/>
       <c r="N40" s="181"/>
       <c r="O40" s="181"/>
@@ -58551,6 +58543,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="7kZ8XDeVMysEOV7IfBeWPhMAFoHFvyoKbjmje3SJ/Wa45BqhNoQ/Eoy2HDxSqxPIUlK7ucngY8t2oyJGu72bpw==" saltValue="dHWQVBt7GS20lA85f3EyAg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="18">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B5:O5"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A34:L34"/>
@@ -58559,16 +58561,6 @@
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="H40:L40"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="B5:O5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A33" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -58611,50 +58603,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="219" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222"/>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222"/>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222"/>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
     </row>
     <row r="2" spans="1:1024" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="223" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="223"/>
-      <c r="C2" s="223"/>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="223"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
-      <c r="M2" s="223"/>
+      <c r="A2" s="220" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="220"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="220"/>
+      <c r="J2" s="220"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="220"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -58669,20 +58661,20 @@
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A3" s="224" t="s">
+      <c r="A3" s="221" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="224"/>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
-      <c r="E3" s="224"/>
-      <c r="F3" s="224"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="224"/>
-      <c r="I3" s="224"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
+      <c r="B3" s="221"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="221"/>
+      <c r="J3" s="221"/>
+      <c r="K3" s="221"/>
+      <c r="L3" s="221"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -58701,41 +58693,41 @@
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="217" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="217"/>
+      <c r="B4" s="218" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
     </row>
     <row r="5" spans="1:1024" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="225" t="str">
+      <c r="B5" s="222" t="str">
         <f>CONCATENATE(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,O38,P38,Q38,R38,S38,T38,U38,V38,W38,X38,Y38,Z38,AA38,AB38,AC38,AD38,AE38,AF38,AG38,AH38,AI38,AJ38,AK38)</f>
         <v>010000100100001000010000000100010011010111100111001100100000000000000000000000000010011100000000101111100101010100000000000000000000000000000000</v>
       </c>
-      <c r="C5" s="225"/>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
-      <c r="M5" s="225"/>
-      <c r="N5" s="225"/>
-      <c r="O5" s="225"/>
+      <c r="C5" s="222"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="222"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -59463,30 +59455,30 @@
       <c r="AMN20" s="1"/>
     </row>
     <row r="21" spans="1:1028" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="226"/>
-      <c r="B21" s="226"/>
-      <c r="C21" s="226"/>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="226"/>
-      <c r="I21" s="226"/>
-      <c r="J21" s="226"/>
-      <c r="K21" s="226"/>
-      <c r="L21" s="226"/>
+      <c r="A21" s="223"/>
+      <c r="B21" s="223"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="223"/>
+      <c r="I21" s="223"/>
+      <c r="J21" s="223"/>
+      <c r="K21" s="223"/>
+      <c r="L21" s="223"/>
     </row>
     <row r="22" spans="1:1028" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="226" t="s">
-        <v>146</v>
-      </c>
-      <c r="B22" s="226"/>
-      <c r="C22" s="226"/>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="226"/>
+      <c r="A22" s="223" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="223"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="223"/>
       <c r="I22" s="43"/>
       <c r="J22" s="43"/>
       <c r="K22" s="43"/>
@@ -59576,78 +59568,78 @@
       <c r="A28" s="43"/>
     </row>
     <row r="29" spans="1:1028" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="226"/>
-      <c r="B29" s="226"/>
-      <c r="C29" s="226"/>
-      <c r="D29" s="226"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="226"/>
-      <c r="G29" s="226"/>
-      <c r="H29" s="226"/>
-      <c r="I29" s="226"/>
-      <c r="J29" s="226"/>
-      <c r="K29" s="226"/>
-      <c r="L29" s="226"/>
+      <c r="A29" s="223"/>
+      <c r="B29" s="223"/>
+      <c r="C29" s="223"/>
+      <c r="D29" s="223"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="223"/>
+      <c r="G29" s="223"/>
+      <c r="H29" s="223"/>
+      <c r="I29" s="223"/>
+      <c r="J29" s="223"/>
+      <c r="K29" s="223"/>
+      <c r="L29" s="223"/>
     </row>
     <row r="30" spans="1:1028" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="226"/>
-      <c r="B30" s="226"/>
-      <c r="C30" s="226"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="226"/>
-      <c r="F30" s="226"/>
-      <c r="G30" s="226"/>
-      <c r="H30" s="226"/>
-      <c r="I30" s="226"/>
-      <c r="J30" s="226"/>
-      <c r="K30" s="226"/>
-      <c r="L30" s="226"/>
+      <c r="A30" s="223"/>
+      <c r="B30" s="223"/>
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="223"/>
+      <c r="I30" s="223"/>
+      <c r="J30" s="223"/>
+      <c r="K30" s="223"/>
+      <c r="L30" s="223"/>
     </row>
     <row r="31" spans="1:1028" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="226"/>
-      <c r="B31" s="226"/>
-      <c r="C31" s="226"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="226"/>
-      <c r="I31" s="226"/>
-      <c r="J31" s="226"/>
-      <c r="K31" s="226"/>
-      <c r="L31" s="226"/>
+      <c r="A31" s="223"/>
+      <c r="B31" s="223"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="223"/>
+      <c r="I31" s="223"/>
+      <c r="J31" s="223"/>
+      <c r="K31" s="223"/>
+      <c r="L31" s="223"/>
     </row>
     <row r="32" spans="1:1028" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="227" t="s">
+      <c r="A32" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="227"/>
-      <c r="C32" s="227"/>
-      <c r="D32" s="227"/>
-      <c r="E32" s="227"/>
-      <c r="F32" s="227"/>
-      <c r="G32" s="227"/>
-      <c r="H32" s="227"/>
-      <c r="I32" s="227"/>
-      <c r="J32" s="227"/>
-      <c r="K32" s="227"/>
-      <c r="L32" s="227"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="224"/>
+      <c r="J32" s="224"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="224"/>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A33" s="218" t="s">
+      <c r="A33" s="217" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="218"/>
-      <c r="C33" s="218"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="218"/>
-      <c r="F33" s="218"/>
-      <c r="G33" s="218"/>
-      <c r="H33" s="218"/>
-      <c r="I33" s="218"/>
-      <c r="J33" s="218"/>
-      <c r="K33" s="218"/>
-      <c r="L33" s="218"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="217"/>
+      <c r="L33" s="217"/>
       <c r="M33" s="39"/>
       <c r="N33" s="39"/>
       <c r="O33" s="39"/>
@@ -59656,20 +59648,20 @@
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A34" s="218" t="s">
+      <c r="A34" s="217" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="218"/>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
+      <c r="B34" s="217"/>
+      <c r="C34" s="217"/>
+      <c r="D34" s="217"/>
+      <c r="E34" s="217"/>
+      <c r="F34" s="217"/>
+      <c r="G34" s="217"/>
+      <c r="H34" s="217"/>
+      <c r="I34" s="217"/>
+      <c r="J34" s="217"/>
+      <c r="K34" s="217"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="39"/>
       <c r="N34" s="39"/>
       <c r="O34" s="39"/>
@@ -59678,33 +59670,33 @@
       <c r="R34" s="2"/>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A35" s="219" t="s">
+      <c r="A35" s="225" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="219"/>
-      <c r="C35" s="219"/>
-      <c r="D35" s="219"/>
-      <c r="E35" s="219"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="219"/>
-      <c r="H35" s="219"/>
-      <c r="I35" s="219"/>
-      <c r="J35" s="219"/>
-      <c r="K35" s="219"/>
-      <c r="L35" s="219"/>
-      <c r="M35" s="219"/>
-      <c r="N35" s="219"/>
-      <c r="O35" s="219"/>
-      <c r="P35" s="219"/>
-      <c r="Q35" s="219"/>
-      <c r="R35" s="219"/>
-      <c r="S35" s="219"/>
-      <c r="T35" s="219"/>
-      <c r="U35" s="219"/>
-      <c r="V35" s="219"/>
-      <c r="W35" s="219"/>
-      <c r="X35" s="219"/>
-      <c r="Y35" s="219"/>
+      <c r="B35" s="225"/>
+      <c r="C35" s="225"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
+      <c r="M35" s="225"/>
+      <c r="N35" s="225"/>
+      <c r="O35" s="225"/>
+      <c r="P35" s="225"/>
+      <c r="Q35" s="225"/>
+      <c r="R35" s="225"/>
+      <c r="S35" s="225"/>
+      <c r="T35" s="225"/>
+      <c r="U35" s="225"/>
+      <c r="V35" s="225"/>
+      <c r="W35" s="225"/>
+      <c r="X35" s="225"/>
+      <c r="Y35" s="225"/>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36" s="40" t="s">
@@ -60137,26 +60129,26 @@
       <c r="P39" s="39"/>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A40" s="220" t="s">
+      <c r="A40" s="226" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="220"/>
-      <c r="C40" s="215" t="s">
+      <c r="B40" s="226"/>
+      <c r="C40" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="215"/>
-      <c r="E40" s="215"/>
-      <c r="F40" s="221" t="s">
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="G40" s="221"/>
-      <c r="H40" s="215" t="s">
+      <c r="G40" s="227"/>
+      <c r="H40" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="I40" s="215"/>
-      <c r="J40" s="215"/>
-      <c r="K40" s="215"/>
-      <c r="L40" s="215"/>
+      <c r="I40" s="210"/>
+      <c r="J40" s="210"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="210"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
@@ -60174,6 +60166,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="eFa58GrenFvcHbLaQIFmVuhhnrR8jj4DG03ME65ysoCwUQZAGbuAnffOQJoIYNsBEuI4x5YP6v5VE/nmEl5Q+A==" saltValue="fBjNfZsxcyhm2+yZXBVQ7A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="18">
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A35:Y35"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:L40"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A2:M2"/>
@@ -60186,12 +60184,6 @@
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A35:Y35"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:L40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A33" r:id="rId1" xr:uid="{1BB1AF57-3B7A-4815-A057-F1B99FE08DBF}"/>
@@ -60232,50 +60224,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="219" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222"/>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222"/>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222"/>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
     </row>
     <row r="2" spans="1:1024" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="223" t="s">
+      <c r="A2" s="220" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="223"/>
-      <c r="C2" s="223"/>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="223"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
-      <c r="M2" s="223"/>
+      <c r="B2" s="220"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="220"/>
+      <c r="J2" s="220"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="220"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -60290,20 +60282,20 @@
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A3" s="224" t="s">
+      <c r="A3" s="221" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="224"/>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
-      <c r="E3" s="224"/>
-      <c r="F3" s="224"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="224"/>
-      <c r="I3" s="224"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
+      <c r="B3" s="221"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="221"/>
+      <c r="J3" s="221"/>
+      <c r="K3" s="221"/>
+      <c r="L3" s="221"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -60322,41 +60314,41 @@
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="218" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="217"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
     </row>
     <row r="5" spans="1:1024" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="225" t="str">
+      <c r="B5" s="222" t="str">
         <f>CONCATENATE(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,O38,P38,Q38,R38,S38,T38,U38,V38,W38,X38,Y38,Z38,AA38,AB38,AC38,AD38,AE38,AF38,AG38,AH38,AI38,AJ38,AK38)</f>
         <v>100000000011110111001001100101010000000000110010000000000000000011111111111111001011000000000000000000000000000000000000000000000000000000000000</v>
       </c>
-      <c r="C5" s="225"/>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
-      <c r="M5" s="225"/>
-      <c r="N5" s="225"/>
-      <c r="O5" s="225"/>
+      <c r="C5" s="222"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="222"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -62136,32 +62128,32 @@
       <c r="AMJ20"/>
     </row>
     <row r="21" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="226" t="s">
+      <c r="A21" s="223" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="226"/>
-      <c r="C21" s="226"/>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="226"/>
-      <c r="I21" s="226"/>
-      <c r="J21" s="226"/>
-      <c r="K21" s="226"/>
-      <c r="L21" s="226"/>
+      <c r="B21" s="223"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="223"/>
+      <c r="I21" s="223"/>
+      <c r="J21" s="223"/>
+      <c r="K21" s="223"/>
+      <c r="L21" s="223"/>
     </row>
     <row r="22" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="226" t="s">
+      <c r="A22" s="223" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="226"/>
-      <c r="C22" s="226"/>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="226"/>
+      <c r="B22" s="223"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="223"/>
       <c r="J22" s="48" t="s">
         <v>64</v>
       </c>
@@ -62256,78 +62248,78 @@
       </c>
     </row>
     <row r="29" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="226"/>
-      <c r="B29" s="226"/>
-      <c r="C29" s="226"/>
-      <c r="D29" s="226"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="226"/>
-      <c r="G29" s="226"/>
-      <c r="H29" s="226"/>
-      <c r="I29" s="226"/>
-      <c r="J29" s="226"/>
-      <c r="K29" s="226"/>
-      <c r="L29" s="226"/>
+      <c r="A29" s="223"/>
+      <c r="B29" s="223"/>
+      <c r="C29" s="223"/>
+      <c r="D29" s="223"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="223"/>
+      <c r="G29" s="223"/>
+      <c r="H29" s="223"/>
+      <c r="I29" s="223"/>
+      <c r="J29" s="223"/>
+      <c r="K29" s="223"/>
+      <c r="L29" s="223"/>
     </row>
     <row r="30" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="226"/>
-      <c r="B30" s="226"/>
-      <c r="C30" s="226"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="226"/>
-      <c r="F30" s="226"/>
-      <c r="G30" s="226"/>
-      <c r="H30" s="226"/>
-      <c r="I30" s="226"/>
-      <c r="J30" s="226"/>
-      <c r="K30" s="226"/>
-      <c r="L30" s="226"/>
+      <c r="A30" s="223"/>
+      <c r="B30" s="223"/>
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="223"/>
+      <c r="I30" s="223"/>
+      <c r="J30" s="223"/>
+      <c r="K30" s="223"/>
+      <c r="L30" s="223"/>
     </row>
     <row r="31" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="226"/>
-      <c r="B31" s="226"/>
-      <c r="C31" s="226"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="226"/>
-      <c r="I31" s="226"/>
-      <c r="J31" s="226"/>
-      <c r="K31" s="226"/>
-      <c r="L31" s="226"/>
+      <c r="A31" s="223"/>
+      <c r="B31" s="223"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="223"/>
+      <c r="I31" s="223"/>
+      <c r="J31" s="223"/>
+      <c r="K31" s="223"/>
+      <c r="L31" s="223"/>
     </row>
     <row r="32" spans="1:1024" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="227" t="s">
+      <c r="A32" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="227"/>
-      <c r="C32" s="227"/>
-      <c r="D32" s="227"/>
-      <c r="E32" s="227"/>
-      <c r="F32" s="227"/>
-      <c r="G32" s="227"/>
-      <c r="H32" s="227"/>
-      <c r="I32" s="227"/>
-      <c r="J32" s="227"/>
-      <c r="K32" s="227"/>
-      <c r="L32" s="227"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="224"/>
+      <c r="J32" s="224"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="224"/>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A33" s="218" t="s">
+      <c r="A33" s="217" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="218"/>
-      <c r="C33" s="218"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="218"/>
-      <c r="F33" s="218"/>
-      <c r="G33" s="218"/>
-      <c r="H33" s="218"/>
-      <c r="I33" s="218"/>
-      <c r="J33" s="218"/>
-      <c r="K33" s="218"/>
-      <c r="L33" s="218"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="217"/>
+      <c r="L33" s="217"/>
       <c r="M33" s="39"/>
       <c r="N33" s="39"/>
       <c r="O33" s="39"/>
@@ -62336,20 +62328,20 @@
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A34" s="218" t="s">
+      <c r="A34" s="217" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="218"/>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
+      <c r="B34" s="217"/>
+      <c r="C34" s="217"/>
+      <c r="D34" s="217"/>
+      <c r="E34" s="217"/>
+      <c r="F34" s="217"/>
+      <c r="G34" s="217"/>
+      <c r="H34" s="217"/>
+      <c r="I34" s="217"/>
+      <c r="J34" s="217"/>
+      <c r="K34" s="217"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="39"/>
       <c r="N34" s="39"/>
       <c r="O34" s="39"/>
@@ -62358,33 +62350,33 @@
       <c r="R34" s="2"/>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A35" s="219" t="s">
+      <c r="A35" s="225" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="219"/>
-      <c r="C35" s="219"/>
-      <c r="D35" s="219"/>
-      <c r="E35" s="219"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="219"/>
-      <c r="H35" s="219"/>
-      <c r="I35" s="219"/>
-      <c r="J35" s="219"/>
-      <c r="K35" s="219"/>
-      <c r="L35" s="219"/>
-      <c r="M35" s="219"/>
-      <c r="N35" s="219"/>
-      <c r="O35" s="219"/>
-      <c r="P35" s="219"/>
-      <c r="Q35" s="219"/>
-      <c r="R35" s="219"/>
-      <c r="S35" s="219"/>
-      <c r="T35" s="219"/>
-      <c r="U35" s="219"/>
-      <c r="V35" s="219"/>
-      <c r="W35" s="219"/>
-      <c r="X35" s="219"/>
-      <c r="Y35" s="219"/>
+      <c r="B35" s="225"/>
+      <c r="C35" s="225"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
+      <c r="M35" s="225"/>
+      <c r="N35" s="225"/>
+      <c r="O35" s="225"/>
+      <c r="P35" s="225"/>
+      <c r="Q35" s="225"/>
+      <c r="R35" s="225"/>
+      <c r="S35" s="225"/>
+      <c r="T35" s="225"/>
+      <c r="U35" s="225"/>
+      <c r="V35" s="225"/>
+      <c r="W35" s="225"/>
+      <c r="X35" s="225"/>
+      <c r="Y35" s="225"/>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="40" t="s">
@@ -62815,26 +62807,26 @@
       <c r="P39" s="39"/>
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A40" s="220" t="s">
+      <c r="A40" s="226" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="220"/>
-      <c r="C40" s="215" t="s">
+      <c r="B40" s="226"/>
+      <c r="C40" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="215"/>
-      <c r="E40" s="215"/>
-      <c r="F40" s="221" t="s">
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="G40" s="221"/>
-      <c r="H40" s="215" t="s">
+      <c r="G40" s="227"/>
+      <c r="H40" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="I40" s="215"/>
-      <c r="J40" s="215"/>
-      <c r="K40" s="215"/>
-      <c r="L40" s="215"/>
+      <c r="I40" s="210"/>
+      <c r="J40" s="210"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="210"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
@@ -62852,6 +62844,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="PKVumjjiZ43mG96QNLzMZmmP7d4MyFtfN/uUNefRsjSgSQ9X7YVyccvPcJGNMSzGRfpVpk7Y7p+eysYWpEffLw==" saltValue="cX9/x5nMxOkhWlpa5URn0g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="18">
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A35:Y35"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:L40"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A2:M2"/>
@@ -62864,12 +62862,6 @@
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A35:Y35"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:L40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A33" r:id="rId1" xr:uid="{4EB1A306-57DB-4E15-8E56-3C8075C80D2E}"/>
@@ -62911,50 +62903,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="219" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="222"/>
-      <c r="H1" s="222"/>
-      <c r="I1" s="222"/>
-      <c r="J1" s="222"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="222"/>
-      <c r="N1" s="222"/>
-      <c r="O1" s="222"/>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="222"/>
-      <c r="S1" s="222"/>
-      <c r="T1" s="222"/>
-      <c r="U1" s="222"/>
-      <c r="V1" s="222"/>
-      <c r="W1" s="222"/>
-      <c r="X1" s="222"/>
-      <c r="Y1" s="222"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="219"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="219"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="219"/>
+      <c r="V1" s="219"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="219"/>
+      <c r="Y1" s="219"/>
     </row>
     <row r="2" spans="1:1024" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="223" t="s">
+      <c r="A2" s="220" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="223"/>
-      <c r="C2" s="223"/>
-      <c r="D2" s="223"/>
-      <c r="E2" s="223"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="223"/>
-      <c r="H2" s="223"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="223"/>
-      <c r="K2" s="223"/>
-      <c r="L2" s="223"/>
-      <c r="M2" s="223"/>
+      <c r="B2" s="220"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="220"/>
+      <c r="G2" s="220"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="220"/>
+      <c r="J2" s="220"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="220"/>
+      <c r="M2" s="220"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -62969,20 +62961,20 @@
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:1024" x14ac:dyDescent="0.25">
-      <c r="A3" s="224" t="s">
+      <c r="A3" s="221" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="224"/>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
-      <c r="E3" s="224"/>
-      <c r="F3" s="224"/>
-      <c r="G3" s="224"/>
-      <c r="H3" s="224"/>
-      <c r="I3" s="224"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
+      <c r="B3" s="221"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="221"/>
+      <c r="J3" s="221"/>
+      <c r="K3" s="221"/>
+      <c r="L3" s="221"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -63001,41 +62993,41 @@
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="217" t="s">
+      <c r="B4" s="218" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="217"/>
-      <c r="G4" s="217"/>
-      <c r="H4" s="217"/>
-      <c r="I4" s="217"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="217"/>
-      <c r="L4" s="217"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
     </row>
     <row r="5" spans="1:1024" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="225" t="str">
+      <c r="B5" s="222" t="str">
         <f>CONCATENATE(B38,C38,D38,E38,F38,G38,H38,I38,J38,K38,L38,M38,N38,O38,P38,Q38,R38,S38,T38,U38,V38,W38,X38,Y38,Z38,AA38,AB38,AC38,AD38,AE38,AF38,AG38,AH38,AI38,AJ38,AK38)</f>
         <v>110001011000001010100001000010000111000001010000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</v>
       </c>
-      <c r="C5" s="225"/>
-      <c r="D5" s="225"/>
-      <c r="E5" s="225"/>
-      <c r="F5" s="225"/>
-      <c r="G5" s="225"/>
-      <c r="H5" s="225"/>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="225"/>
-      <c r="L5" s="225"/>
-      <c r="M5" s="225"/>
-      <c r="N5" s="225"/>
-      <c r="O5" s="225"/>
+      <c r="C5" s="222"/>
+      <c r="D5" s="222"/>
+      <c r="E5" s="222"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="222"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="222"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="222"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="222"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -64815,32 +64807,32 @@
       <c r="AMJ20"/>
     </row>
     <row r="21" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="226" t="s">
+      <c r="A21" s="223" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="226"/>
-      <c r="C21" s="226"/>
-      <c r="D21" s="226"/>
-      <c r="E21" s="226"/>
-      <c r="F21" s="226"/>
-      <c r="G21" s="226"/>
-      <c r="H21" s="226"/>
-      <c r="I21" s="226"/>
-      <c r="J21" s="226"/>
-      <c r="K21" s="226"/>
-      <c r="L21" s="226"/>
+      <c r="B21" s="223"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="223"/>
+      <c r="I21" s="223"/>
+      <c r="J21" s="223"/>
+      <c r="K21" s="223"/>
+      <c r="L21" s="223"/>
     </row>
     <row r="22" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="226" t="s">
+      <c r="A22" s="223" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="226"/>
-      <c r="C22" s="226"/>
-      <c r="D22" s="226"/>
-      <c r="E22" s="226"/>
-      <c r="F22" s="226"/>
-      <c r="G22" s="226"/>
-      <c r="H22" s="226"/>
+      <c r="B22" s="223"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="223"/>
       <c r="J22" s="48" t="s">
         <v>64</v>
       </c>
@@ -64935,78 +64927,78 @@
       </c>
     </row>
     <row r="29" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="226"/>
-      <c r="B29" s="226"/>
-      <c r="C29" s="226"/>
-      <c r="D29" s="226"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="226"/>
-      <c r="G29" s="226"/>
-      <c r="H29" s="226"/>
-      <c r="I29" s="226"/>
-      <c r="J29" s="226"/>
-      <c r="K29" s="226"/>
-      <c r="L29" s="226"/>
+      <c r="A29" s="223"/>
+      <c r="B29" s="223"/>
+      <c r="C29" s="223"/>
+      <c r="D29" s="223"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="223"/>
+      <c r="G29" s="223"/>
+      <c r="H29" s="223"/>
+      <c r="I29" s="223"/>
+      <c r="J29" s="223"/>
+      <c r="K29" s="223"/>
+      <c r="L29" s="223"/>
     </row>
     <row r="30" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="226"/>
-      <c r="B30" s="226"/>
-      <c r="C30" s="226"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="226"/>
-      <c r="F30" s="226"/>
-      <c r="G30" s="226"/>
-      <c r="H30" s="226"/>
-      <c r="I30" s="226"/>
-      <c r="J30" s="226"/>
-      <c r="K30" s="226"/>
-      <c r="L30" s="226"/>
+      <c r="A30" s="223"/>
+      <c r="B30" s="223"/>
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="223"/>
+      <c r="I30" s="223"/>
+      <c r="J30" s="223"/>
+      <c r="K30" s="223"/>
+      <c r="L30" s="223"/>
     </row>
     <row r="31" spans="1:1024" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="226"/>
-      <c r="B31" s="226"/>
-      <c r="C31" s="226"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="226"/>
-      <c r="G31" s="226"/>
-      <c r="H31" s="226"/>
-      <c r="I31" s="226"/>
-      <c r="J31" s="226"/>
-      <c r="K31" s="226"/>
-      <c r="L31" s="226"/>
+      <c r="A31" s="223"/>
+      <c r="B31" s="223"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="223"/>
+      <c r="I31" s="223"/>
+      <c r="J31" s="223"/>
+      <c r="K31" s="223"/>
+      <c r="L31" s="223"/>
     </row>
     <row r="32" spans="1:1024" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="227" t="s">
+      <c r="A32" s="224" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="227"/>
-      <c r="C32" s="227"/>
-      <c r="D32" s="227"/>
-      <c r="E32" s="227"/>
-      <c r="F32" s="227"/>
-      <c r="G32" s="227"/>
-      <c r="H32" s="227"/>
-      <c r="I32" s="227"/>
-      <c r="J32" s="227"/>
-      <c r="K32" s="227"/>
-      <c r="L32" s="227"/>
+      <c r="B32" s="224"/>
+      <c r="C32" s="224"/>
+      <c r="D32" s="224"/>
+      <c r="E32" s="224"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="224"/>
+      <c r="H32" s="224"/>
+      <c r="I32" s="224"/>
+      <c r="J32" s="224"/>
+      <c r="K32" s="224"/>
+      <c r="L32" s="224"/>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A33" s="218" t="s">
+      <c r="A33" s="217" t="s">
         <v>52</v>
       </c>
-      <c r="B33" s="218"/>
-      <c r="C33" s="218"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="218"/>
-      <c r="F33" s="218"/>
-      <c r="G33" s="218"/>
-      <c r="H33" s="218"/>
-      <c r="I33" s="218"/>
-      <c r="J33" s="218"/>
-      <c r="K33" s="218"/>
-      <c r="L33" s="218"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="217"/>
+      <c r="G33" s="217"/>
+      <c r="H33" s="217"/>
+      <c r="I33" s="217"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="217"/>
+      <c r="L33" s="217"/>
       <c r="M33" s="39"/>
       <c r="N33" s="39"/>
       <c r="O33" s="39"/>
@@ -65015,20 +65007,20 @@
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A34" s="218" t="s">
+      <c r="A34" s="217" t="s">
         <v>53</v>
       </c>
-      <c r="B34" s="218"/>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="218"/>
-      <c r="I34" s="218"/>
-      <c r="J34" s="218"/>
-      <c r="K34" s="218"/>
-      <c r="L34" s="218"/>
+      <c r="B34" s="217"/>
+      <c r="C34" s="217"/>
+      <c r="D34" s="217"/>
+      <c r="E34" s="217"/>
+      <c r="F34" s="217"/>
+      <c r="G34" s="217"/>
+      <c r="H34" s="217"/>
+      <c r="I34" s="217"/>
+      <c r="J34" s="217"/>
+      <c r="K34" s="217"/>
+      <c r="L34" s="217"/>
       <c r="M34" s="39"/>
       <c r="N34" s="39"/>
       <c r="O34" s="39"/>
@@ -65037,33 +65029,33 @@
       <c r="R34" s="2"/>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A35" s="219" t="s">
+      <c r="A35" s="225" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="219"/>
-      <c r="C35" s="219"/>
-      <c r="D35" s="219"/>
-      <c r="E35" s="219"/>
-      <c r="F35" s="219"/>
-      <c r="G35" s="219"/>
-      <c r="H35" s="219"/>
-      <c r="I35" s="219"/>
-      <c r="J35" s="219"/>
-      <c r="K35" s="219"/>
-      <c r="L35" s="219"/>
-      <c r="M35" s="219"/>
-      <c r="N35" s="219"/>
-      <c r="O35" s="219"/>
-      <c r="P35" s="219"/>
-      <c r="Q35" s="219"/>
-      <c r="R35" s="219"/>
-      <c r="S35" s="219"/>
-      <c r="T35" s="219"/>
-      <c r="U35" s="219"/>
-      <c r="V35" s="219"/>
-      <c r="W35" s="219"/>
-      <c r="X35" s="219"/>
-      <c r="Y35" s="219"/>
+      <c r="B35" s="225"/>
+      <c r="C35" s="225"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
+      <c r="M35" s="225"/>
+      <c r="N35" s="225"/>
+      <c r="O35" s="225"/>
+      <c r="P35" s="225"/>
+      <c r="Q35" s="225"/>
+      <c r="R35" s="225"/>
+      <c r="S35" s="225"/>
+      <c r="T35" s="225"/>
+      <c r="U35" s="225"/>
+      <c r="V35" s="225"/>
+      <c r="W35" s="225"/>
+      <c r="X35" s="225"/>
+      <c r="Y35" s="225"/>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="40" t="s">
@@ -65494,26 +65486,26 @@
       <c r="P39" s="39"/>
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A40" s="220" t="s">
+      <c r="A40" s="226" t="s">
         <v>29</v>
       </c>
-      <c r="B40" s="220"/>
-      <c r="C40" s="215" t="s">
+      <c r="B40" s="226"/>
+      <c r="C40" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="D40" s="215"/>
-      <c r="E40" s="215"/>
-      <c r="F40" s="221" t="s">
+      <c r="D40" s="210"/>
+      <c r="E40" s="210"/>
+      <c r="F40" s="227" t="s">
         <v>31</v>
       </c>
-      <c r="G40" s="221"/>
-      <c r="H40" s="215" t="s">
+      <c r="G40" s="227"/>
+      <c r="H40" s="210" t="s">
         <v>32</v>
       </c>
-      <c r="I40" s="215"/>
-      <c r="J40" s="215"/>
-      <c r="K40" s="215"/>
-      <c r="L40" s="215"/>
+      <c r="I40" s="210"/>
+      <c r="J40" s="210"/>
+      <c r="K40" s="210"/>
+      <c r="L40" s="210"/>
       <c r="M40" s="39"/>
       <c r="N40" s="39"/>
       <c r="O40" s="39"/>
@@ -65531,6 +65523,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="a0P1JVo6TQDgUlTlA/jLaLJd8wbQYImGQg1vXvSXRApk3FtCbh9ruQc8Qk65GmyO/e3kRCkvw6YqvfVQckFDcA==" saltValue="ha5iHlr6CcgkbjV2wxeDyw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="18">
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A35:Y35"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:L40"/>
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A2:M2"/>
@@ -65543,12 +65541,6 @@
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A31:L31"/>
     <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A35:Y35"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:L40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A33" r:id="rId1" xr:uid="{FE64ED39-1A54-4E2E-84A4-51427F2441B8}"/>
